--- a/marketing_report/outputs/Cursos/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Cursos/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,13 +464,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23084310717</t>
+          <t>14876203835</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -498,17 +498,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14876203835</t>
+          <t>23084310717</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -517,17 +517,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14909096324</t>
+          <t>8419948319</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -536,17 +536,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23277494379</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -555,19 +555,133 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8419948319</t>
+          <t>14909096324</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14896121927</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14909223761</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15357460006</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>19230946036</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20612364611</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>23277494379</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>100</v>
       </c>
     </row>
@@ -619,13 +733,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -642,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,13 +793,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -694,17 +808,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>relaciones internacionales carrera</t>
+          <t>universidad catolica de salta</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -713,17 +827,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>universidad catolica de salta</t>
+          <t>carreras universitarias</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -732,19 +846,228 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>universidad siglo 21</t>
+          <t>relaciones internacionales carrera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>universidad</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>carrera de higiene y seguridad</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>carreras cortas</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ciberseguridad carrera</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>las carreras universitarias</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>licenciatura en administracion de empresas</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mineria en argentina</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>recursos humanos carrera</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>siglo 21</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ucasal carreras a distancia</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>universidad católica de salta</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Cursos/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Cursos/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -33,42 +33,12 @@
     <t>Tasa_%</t>
   </si>
   <si>
+    <t>14876203835</t>
+  </si>
+  <si>
     <t>21676468921</t>
   </si>
   <si>
-    <t>14876203835</t>
-  </si>
-  <si>
-    <t>23084310717</t>
-  </si>
-  <si>
-    <t>8419948319</t>
-  </si>
-  <si>
-    <t>14875022827</t>
-  </si>
-  <si>
-    <t>14909096324</t>
-  </si>
-  <si>
-    <t>14896121927</t>
-  </si>
-  <si>
-    <t>14909223761</t>
-  </si>
-  <si>
-    <t>15357460006</t>
-  </si>
-  <si>
-    <t>19230946036</t>
-  </si>
-  <si>
-    <t>20612364611</t>
-  </si>
-  <si>
-    <t>23277494379</t>
-  </si>
-  <si>
     <t>UtmMedium</t>
   </si>
   <si>
@@ -79,48 +49,6 @@
   </si>
   <si>
     <t>ucasal</t>
-  </si>
-  <si>
-    <t>universidad catolica de salta</t>
-  </si>
-  <si>
-    <t>carreras universitarias</t>
-  </si>
-  <si>
-    <t>relaciones internacionales carrera</t>
-  </si>
-  <si>
-    <t>universidad</t>
-  </si>
-  <si>
-    <t>carrera de higiene y seguridad</t>
-  </si>
-  <si>
-    <t>carreras cortas</t>
-  </si>
-  <si>
-    <t>ciberseguridad carrera</t>
-  </si>
-  <si>
-    <t>las carreras universitarias</t>
-  </si>
-  <si>
-    <t>licenciatura en administracion de empresas</t>
-  </si>
-  <si>
-    <t>mineria en argentina</t>
-  </si>
-  <si>
-    <t>recursos humanos carrera</t>
-  </si>
-  <si>
-    <t>siglo 21</t>
-  </si>
-  <si>
-    <t>ucasal carreras a distancia</t>
-  </si>
-  <si>
-    <t>universidad católica de salta</t>
   </si>
 </sst>
 </file>
@@ -478,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -503,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -520,185 +448,15 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
         <v>100</v>
       </c>
     </row>
@@ -714,7 +472,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -731,16 +489,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -753,12 +511,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -775,256 +533,18 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
         <v>100</v>
       </c>
     </row>
